--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327544</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327544</v>
       </c>
       <c r="B2" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327544</v>
       </c>
       <c r="B2" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130327544</v>
       </c>
       <c r="B2" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131143231</v>
       </c>
       <c r="B3" t="n">
-        <v>75351</v>
+        <v>75352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131143231</v>
       </c>
       <c r="B3" t="n">
-        <v>75352</v>
+        <v>75354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131143231</v>
       </c>
       <c r="B3" t="n">
-        <v>75354</v>
+        <v>75355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131143231</v>
       </c>
       <c r="B3" t="n">
-        <v>75355</v>
+        <v>75356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131143231</v>
       </c>
       <c r="B3" t="n">
-        <v>75356</v>
+        <v>75359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131143231</v>
       </c>
       <c r="B3" t="n">
-        <v>75359</v>
+        <v>75360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>131143231</v>
       </c>
       <c r="B3" t="n">
-        <v>75360</v>
+        <v>75366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51595-2025 artfynd.xlsx
+++ b/artfynd/A 51595-2025 artfynd.xlsx
@@ -675,50 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130327544</v>
+        <v>131143231</v>
       </c>
       <c r="B2" t="n">
-        <v>57053</v>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -756,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -798,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131143231</v>
+        <v>130327544</v>
       </c>
       <c r="B3" t="n">
-        <v>75366</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,26 +787,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -866,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
